--- a/data/dividends_info_20260825.xlsx
+++ b/data/dividends_info_20260825.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>42.71500015258789</v>
+        <v>42.55500030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2106988169928576</v>
+        <v>0.2114910101153346</v>
       </c>
       <c r="J2" t="n">
         <v>202</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.15000152587891</v>
+        <v>66.59999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.042442269685172</v>
+        <v>1.051051075131782</v>
       </c>
       <c r="J3" t="n">
         <v>181</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.319999694824219</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6437768451142812</v>
+        <v>0.6451612770908873</v>
       </c>
       <c r="J4" t="n">
         <v>111</v>
@@ -663,8 +663,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.4900000095367432</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8163265147242933</v>
+      </c>
       <c r="J5" t="n">
         <v>111</v>
       </c>
@@ -707,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42.71500015258789</v>
+        <v>42.55500030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2106988169928576</v>
+        <v>0.2114910101153346</v>
       </c>
       <c r="J6" t="n">
         <v>111</v>
@@ -754,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.125</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.623529411764706</v>
       </c>
       <c r="J7" t="n">
         <v>90</v>
@@ -801,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.59000015258789</v>
+        <v>23.26499938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.14455276919691</v>
+        <v>1.160541616520025</v>
       </c>
       <c r="J8" t="n">
         <v>90</v>
@@ -848,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>23.30999946594238</v>
       </c>
       <c r="I9" t="n">
-        <v>2.565217391304348</v>
+        <v>2.531102589092862</v>
       </c>
       <c r="J9" t="n">
         <v>90</v>
@@ -895,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.840000152587891</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>3.424657444766908</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J10" t="n">
         <v>83</v>
@@ -942,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.40999984741211</v>
+        <v>10.47000026702881</v>
       </c>
       <c r="I11" t="n">
-        <v>4.41882811472235</v>
+        <v>4.393505141051342</v>
       </c>
       <c r="J11" t="n">
         <v>62</v>
@@ -989,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.400000095367432</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J12" t="n">
         <v>55</v>
@@ -1035,8 +1039,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.4900000095367432</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8163265147242933</v>
+      </c>
       <c r="J13" t="n">
         <v>55</v>
       </c>
@@ -1126,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.019999980926514</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7569721144298999</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J15" t="n">
         <v>34</v>
@@ -1173,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.59000015258789</v>
+        <v>23.26499938964844</v>
       </c>
       <c r="I16" t="n">
-        <v>1.14455276919691</v>
+        <v>1.160541616520025</v>
       </c>
       <c r="J16" t="n">
         <v>27</v>
@@ -1220,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.052000045776367</v>
+        <v>2.084000110626221</v>
       </c>
       <c r="I17" t="n">
-        <v>2.777777715810637</v>
+        <v>2.735124614886517</v>
       </c>
       <c r="J17" t="n">
         <v>27</v>
@@ -1267,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>42.71500015258789</v>
+        <v>42.55500030517578</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2106988169928576</v>
+        <v>0.2114910101153346</v>
       </c>
       <c r="J18" t="n">
         <v>27</v>
@@ -1314,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90.05000305175781</v>
+        <v>90.94999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.476957195920981</v>
+        <v>1.462341995192013</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
@@ -1361,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.079999923706055</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="I20" t="n">
-        <v>4.934210588231972</v>
+        <v>4.885993591588033</v>
       </c>
       <c r="J20" t="n">
         <v>20</v>
@@ -1407,8 +1415,12 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.4900000095367432</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8163265147242933</v>
+      </c>
       <c r="J21" t="n">
         <v>-1</v>
       </c>
@@ -1498,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.980000019073486</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J23" t="n">
         <v>-22</v>
@@ -1592,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.549999952316284</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I25" t="n">
-        <v>5.802705990860621</v>
+        <v>5.871785758728343</v>
       </c>
       <c r="J25" t="n">
         <v>-22</v>
@@ -1639,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.920000076293945</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I26" t="n">
-        <v>4.222972918549448</v>
+        <v>4.187604837285504</v>
       </c>
       <c r="J26" t="n">
         <v>-29</v>
@@ -3419,7 +3431,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3429,14 +3441,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3453,7 +3465,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3470,7 +3482,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3487,7 +3499,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3504,7 +3516,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3521,7 +3533,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3531,14 +3543,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3555,7 +3567,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3572,7 +3584,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3582,7 +3594,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3737,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3735,14 +3747,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3780,367 +3792,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ELSA Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Egomnia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Giglio.com S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Intred S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>POWERSOFT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sicily by Car S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Softlab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>eVISO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rino petino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>